--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2906-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2906-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{80A38045-B828-4720-85FF-F2B136981308}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6CB2D713-F483-45B1-AE99-5B747A9B61B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{653499F6-47E2-4998-BC1F-9888B6AAE97B}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{E882F314-AF1C-41CC-BC3C-5069B91C2EE6}"/>
   </bookViews>
   <sheets>
     <sheet name="2906-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1598,27 +1598,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD803C93-CDC9-4EDF-9037-7455EAE2A0BB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74EE6588-D47D-40E7-B5B1-29E205C7B357}">
   <dimension ref="A1:X46"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="4" width="6.25" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1652,7 +1651,7 @@
       <c r="W1" s="32"/>
       <c r="X1" s="24"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1688,7 +1687,7 @@
       <c r="W2" s="34"/>
       <c r="X2" s="35"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1740,7 +1739,7 @@
       </c>
       <c r="X3" s="38"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1808,7 +1807,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="39">
         <v>2024</v>
       </c>
@@ -1880,7 +1879,7 @@
         <v>4.76</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="41">
         <v>2023</v>
       </c>
@@ -1952,7 +1951,7 @@
         <v>3.56</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="39">
         <v>2022</v>
       </c>
@@ -2024,7 +2023,7 @@
         <v>3.85</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="41">
         <v>2021</v>
       </c>
@@ -2096,7 +2095,7 @@
         <v>2.91</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="39">
         <v>2020</v>
       </c>
@@ -2168,7 +2167,7 @@
         <v>2.36</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="41">
         <v>2019</v>
       </c>
@@ -2240,7 +2239,7 @@
         <v>3.33</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="39">
         <v>2018</v>
       </c>
@@ -2312,7 +2311,7 @@
         <v>4.26</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="41">
         <v>2017</v>
       </c>
@@ -2384,7 +2383,7 @@
         <v>4.3499999999999996</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="39">
         <v>2016</v>
       </c>
@@ -2456,7 +2455,7 @@
         <v>3.86</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="41">
         <v>2015</v>
       </c>
@@ -2528,7 +2527,7 @@
         <v>4.8499999999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="39">
         <v>2014</v>
       </c>
@@ -2600,7 +2599,7 @@
         <v>7.96</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="41">
         <v>2013</v>
       </c>
@@ -2672,7 +2671,7 @@
         <v>6.57</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="39">
         <v>2012</v>
       </c>
@@ -2744,7 +2743,7 @@
         <v>5.71</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="41">
         <v>2011</v>
       </c>
@@ -2816,7 +2815,7 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="39">
         <v>2010</v>
       </c>
@@ -2888,7 +2887,7 @@
         <v>7.81</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="41">
         <v>2009</v>
       </c>
@@ -2960,7 +2959,7 @@
         <v>7.46</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="39">
         <v>2008</v>
       </c>
@@ -3032,7 +3031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="41">
         <v>2007</v>
       </c>
@@ -3104,7 +3103,7 @@
         <v>11.1</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="39">
         <v>2006</v>
       </c>
@@ -3176,7 +3175,7 @@
         <v>7.63</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="41">
         <v>2005</v>
       </c>
@@ -3248,7 +3247,7 @@
         <v>8.27</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="39">
         <v>2004</v>
       </c>
@@ -3320,7 +3319,7 @@
         <v>11.2</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="41">
         <v>2003</v>
       </c>
@@ -3392,7 +3391,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="39">
         <v>2002</v>
       </c>
@@ -3464,7 +3463,7 @@
         <v>9.76</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="41">
         <v>2001</v>
       </c>
@@ -3536,7 +3535,7 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="39">
         <v>2000</v>
       </c>
@@ -3608,7 +3607,7 @@
         <v>7.89</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="41">
         <v>1999</v>
       </c>
@@ -3680,7 +3679,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="39">
         <v>1998</v>
       </c>
@@ -3752,7 +3751,7 @@
         <v>16.100000000000001</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="41">
         <v>1997</v>
       </c>
@@ -3824,7 +3823,7 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="43">
         <v>1996</v>
       </c>
@@ -3896,7 +3895,7 @@
         <v>9.57</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="45"/>
       <c r="B34" s="46"/>
       <c r="C34" s="20" t="s">
@@ -3924,7 +3923,7 @@
       <c r="W34" s="52"/>
       <c r="X34" s="48"/>
     </row>
-    <row r="35" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="41">
         <v>1995</v>
       </c>
@@ -3996,7 +3995,7 @@
         <v>11.7</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="39">
         <v>1994</v>
       </c>
@@ -4068,7 +4067,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="41">
         <v>1993</v>
       </c>
@@ -4140,7 +4139,7 @@
         <v>5.08</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="39">
         <v>1992</v>
       </c>
@@ -4212,7 +4211,7 @@
         <v>7.32</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="41">
         <v>1991</v>
       </c>
@@ -4284,7 +4283,7 @@
         <v>3.03</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="39">
         <v>1990</v>
       </c>
@@ -4356,7 +4355,7 @@
         <v>4.8499999999999996</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="53">
         <v>1989</v>
       </c>
@@ -4428,7 +4427,7 @@
         <v>4.8499999999999996</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="55"/>
       <c r="B42" s="56"/>
       <c r="C42" s="22" t="s">
@@ -4456,7 +4455,7 @@
       <c r="W42" s="62"/>
       <c r="X42" s="58"/>
     </row>
-    <row r="43" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="39">
         <v>1988</v>
       </c>
@@ -4528,7 +4527,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="41">
         <v>1987</v>
       </c>
@@ -4600,7 +4599,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="39">
         <v>1986</v>
       </c>
@@ -4672,7 +4671,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="41" t="s">
         <v>66</v>
       </c>
